--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119874946</v>
+        <v>119874944</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,42 +1553,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577781</v>
+        <v>577806</v>
       </c>
       <c r="R10" t="n">
-        <v>7078599</v>
+        <v>7078549</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1623,6 +1619,11 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1635,22 +1636,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119874944</v>
+        <v>119874842</v>
       </c>
       <c r="B11" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,38 +1660,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjön, Tågsjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577806</v>
+        <v>577776</v>
       </c>
       <c r="R11" t="n">
-        <v>7078549</v>
+        <v>7078629</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1725,11 +1730,6 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1742,19 +1742,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119874842</v>
+        <v>119874946</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1789,19 +1789,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tågsjön, Tågsjön, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577776</v>
+        <v>577781</v>
       </c>
       <c r="R12" t="n">
-        <v>7078629</v>
+        <v>7078599</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119874944</v>
+        <v>119874946</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,38 +1553,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577806</v>
+        <v>577781</v>
       </c>
       <c r="R10" t="n">
-        <v>7078549</v>
+        <v>7078599</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1619,11 +1623,6 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1636,12 +1635,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1754,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119874946</v>
+        <v>119874944</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,42 +1765,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577781</v>
+        <v>577806</v>
       </c>
       <c r="R12" t="n">
-        <v>7078599</v>
+        <v>7078549</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1836,6 +1831,11 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1848,12 +1848,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119874946</v>
+        <v>119874842</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1576,19 +1576,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjön, Tågsjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577781</v>
+        <v>577776</v>
       </c>
       <c r="R10" t="n">
-        <v>7078599</v>
+        <v>7078629</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119874842</v>
+        <v>119874944</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,42 +1659,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tågsjön, Tågsjön, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577776</v>
+        <v>577806</v>
       </c>
       <c r="R11" t="n">
-        <v>7078629</v>
+        <v>7078549</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1729,6 +1725,11 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1741,22 +1742,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119874944</v>
+        <v>119874946</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,38 +1766,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577806</v>
+        <v>577781</v>
       </c>
       <c r="R12" t="n">
-        <v>7078549</v>
+        <v>7078599</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1831,11 +1836,6 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1848,12 +1848,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>119874842</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119874944</v>
+        <v>119874946</v>
       </c>
       <c r="B11" t="n">
-        <v>57326</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,38 +1659,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577806</v>
+        <v>577781</v>
       </c>
       <c r="R11" t="n">
-        <v>7078549</v>
+        <v>7078599</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1725,11 +1729,6 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1742,22 +1741,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119874946</v>
+        <v>119874944</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,42 +1765,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577781</v>
+        <v>577806</v>
       </c>
       <c r="R12" t="n">
-        <v>7078599</v>
+        <v>7078549</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1836,6 +1831,11 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1848,12 +1848,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1863,7 +1863,7 @@
         <v>119966839</v>
       </c>
       <c r="B13" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119874842</v>
+        <v>119874946</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1576,19 +1576,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tågsjön, Tågsjön, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577776</v>
+        <v>577781</v>
       </c>
       <c r="R10" t="n">
-        <v>7078629</v>
+        <v>7078599</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119874946</v>
+        <v>119874944</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,42 +1659,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577781</v>
+        <v>577806</v>
       </c>
       <c r="R11" t="n">
-        <v>7078599</v>
+        <v>7078549</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1729,6 +1725,11 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1741,22 +1742,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119874944</v>
+        <v>119874842</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,38 +1766,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjön, Tågsjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577806</v>
+        <v>577776</v>
       </c>
       <c r="R12" t="n">
-        <v>7078549</v>
+        <v>7078629</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1831,11 +1836,6 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1848,12 +1848,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119874944</v>
+        <v>119874842</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,38 +1659,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjön, Tågsjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577806</v>
+        <v>577776</v>
       </c>
       <c r="R11" t="n">
-        <v>7078549</v>
+        <v>7078629</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1725,11 +1729,6 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1742,22 +1741,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119874842</v>
+        <v>119874944</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,42 +1765,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tågsjön, Tågsjön, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577776</v>
+        <v>577806</v>
       </c>
       <c r="R12" t="n">
-        <v>7078629</v>
+        <v>7078549</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1836,6 +1831,11 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1848,12 +1848,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119874946</v>
+        <v>119874842</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1576,19 +1576,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjön, Tågsjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577781</v>
+        <v>577776</v>
       </c>
       <c r="R10" t="n">
-        <v>7078599</v>
+        <v>7078629</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119874842</v>
+        <v>119874944</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,42 +1659,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tågsjön, Tågsjön, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577776</v>
+        <v>577806</v>
       </c>
       <c r="R11" t="n">
-        <v>7078629</v>
+        <v>7078549</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1729,6 +1725,11 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1741,22 +1742,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119874944</v>
+        <v>119874946</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,38 +1766,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577806</v>
+        <v>577781</v>
       </c>
       <c r="R12" t="n">
-        <v>7078549</v>
+        <v>7078599</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1831,11 +1836,6 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1848,12 +1848,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1976,6 +1976,113 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124792925</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>577820</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7078516</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -1981,7 +1981,7 @@
         <v>124792925</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2083,6 +2083,103 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127702684</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>577881</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7078510</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2088,7 +2088,7 @@
         <v>127702684</v>
       </c>
       <c r="B15" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2088,7 +2088,7 @@
         <v>127702684</v>
       </c>
       <c r="B15" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2088,7 +2088,7 @@
         <v>127702684</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2088,7 +2088,7 @@
         <v>127702684</v>
       </c>
       <c r="B15" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2088,7 +2088,7 @@
         <v>127702684</v>
       </c>
       <c r="B15" t="n">
-        <v>57833</v>
+        <v>57844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2180,6 +2180,112 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128787659</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56880</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tågsjön, Tågsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>577754</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7078595</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2 Hone, 1 Hane</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2185,7 +2185,7 @@
         <v>128787659</v>
       </c>
       <c r="B16" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2185,7 +2185,7 @@
         <v>128787659</v>
       </c>
       <c r="B16" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2185,7 +2185,7 @@
         <v>128787659</v>
       </c>
       <c r="B16" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2185,7 +2185,7 @@
         <v>128787659</v>
       </c>
       <c r="B16" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2185,7 +2185,7 @@
         <v>128787659</v>
       </c>
       <c r="B16" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2088,7 +2088,7 @@
         <v>127702684</v>
       </c>
       <c r="B15" t="n">
-        <v>57844</v>
+        <v>58023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2114,6 +2114,14 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119308019</v>
+        <v>124792925</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577771</v>
+        <v>577820</v>
       </c>
       <c r="R2" t="n">
-        <v>7078587</v>
+        <v>7078516</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -759,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119307551</v>
+        <v>127702419</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577771</v>
+        <v>577847</v>
       </c>
       <c r="R3" t="n">
-        <v>7078587</v>
+        <v>7078458</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -861,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,64 +874,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119307978</v>
+        <v>127702684</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577789</v>
+        <v>577881</v>
       </c>
       <c r="R4" t="n">
-        <v>7078578</v>
+        <v>7078510</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -977,12 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119308342</v>
+        <v>119307551</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577773</v>
+        <v>577771</v>
       </c>
       <c r="R5" t="n">
-        <v>7078612</v>
+        <v>7078587</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1114,16 +1079,11 @@
         <v>119308416</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1213,57 +1173,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119340318</v>
+        <v>119874917</v>
       </c>
       <c r="B7" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tågsjön, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577784</v>
+        <v>577820</v>
       </c>
       <c r="R7" t="n">
-        <v>7078576</v>
+        <v>7078594</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,12 +1238,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,64 +1270,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119330920</v>
+        <v>119874944</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577771</v>
+        <v>577806</v>
       </c>
       <c r="R8" t="n">
-        <v>7078637</v>
+        <v>7078549</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1403,12 +1335,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,68 +1360,76 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119339731</v>
+        <v>119966839</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tågsjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577770</v>
+        <v>577772</v>
       </c>
       <c r="R9" t="n">
-        <v>7078632</v>
+        <v>7078585</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1508,12 +1453,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,7 +1467,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1541,42 +1485,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119874842</v>
+        <v>127778773</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1585,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577776</v>
+        <v>577747</v>
       </c>
       <c r="R10" t="n">
-        <v>7078629</v>
+        <v>7078604</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1615,12 +1565,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,50 +1597,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119874944</v>
+        <v>128787659</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjön, Tågsjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577806</v>
+        <v>577754</v>
       </c>
       <c r="R11" t="n">
-        <v>7078549</v>
+        <v>7078595</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1717,17 +1666,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>2 Hone, 1 Hane</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,66 +1691,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119874946</v>
+        <v>119307209</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577781</v>
+        <v>577729</v>
       </c>
       <c r="R12" t="n">
-        <v>7078599</v>
+        <v>7078650</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1828,12 +1768,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,66 +1800,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119966839</v>
+        <v>119340318</v>
       </c>
       <c r="B13" t="n">
-        <v>56532</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tågsjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577772</v>
+        <v>577784</v>
       </c>
       <c r="R13" t="n">
-        <v>7078585</v>
+        <v>7078576</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,12 +1869,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1978,55 +1901,59 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124792925</v>
+        <v>119307978</v>
       </c>
       <c r="B14" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577820</v>
+        <v>577789</v>
       </c>
       <c r="R14" t="n">
-        <v>7078516</v>
+        <v>7078578</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2053,12 +1980,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2085,53 +2012,59 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702684</v>
+        <v>119308019</v>
       </c>
       <c r="B15" t="n">
-        <v>58043</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577881</v>
+        <v>577771</v>
       </c>
       <c r="R15" t="n">
-        <v>7078510</v>
+        <v>7078587</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2158,12 +2091,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2190,49 +2123,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128787659</v>
+        <v>119308342</v>
       </c>
       <c r="B16" t="n">
-        <v>56917</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tågsjön, Tågsjön, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577754</v>
+        <v>577773</v>
       </c>
       <c r="R16" t="n">
-        <v>7078595</v>
+        <v>7078612</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2259,17 +2188,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 Hone, 1 Hane</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,6 +2217,319 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>119330920</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>577771</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7078637</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>119874842</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tågsjön, Tågsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>577776</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7078629</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>119874946</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>577781</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7078599</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119307551</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119308416</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119874917</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119874944</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119966839</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124792925</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127778773</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787659</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1595,6 +1640,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119307209</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,6 +1746,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119340318</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702419</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1898,6 +1958,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702684</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2009,6 +2074,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119307978</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119308019</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2217,6 +2292,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119308342</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2328,6 +2408,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119330920</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2429,6 +2514,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119874842</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2530,8 +2620,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119874946</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2623,6 +2623,339 @@
       <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119874946</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135613481</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>577849</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7078493</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135613481</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135614695</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>577896</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7078499</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135614695</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135614917</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>577902</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7078515</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135614917</t>
         </is>
       </c>
     </row>
@@ -2646,6 +2979,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2631,7 +2631,7 @@
         <v>135613481</v>
       </c>
       <c r="B20" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>135614695</v>
       </c>
       <c r="B21" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>135614917</v>
       </c>
       <c r="B22" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2623,6 +2623,339 @@
       <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119874946</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135613481</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>577849</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7078493</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135613481</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135614695</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>577896</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7078499</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135614695</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135614917</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>577902</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7078515</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135614917</t>
         </is>
       </c>
     </row>
@@ -2646,6 +2979,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2631,7 +2631,7 @@
         <v>135613481</v>
       </c>
       <c r="B20" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>135614695</v>
       </c>
       <c r="B21" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>135614917</v>
       </c>
       <c r="B22" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2631,7 +2631,7 @@
         <v>135613481</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>135614695</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>135614917</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2631,7 +2631,7 @@
         <v>135613481</v>
       </c>
       <c r="B20" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>135614695</v>
       </c>
       <c r="B21" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>135614917</v>
       </c>
       <c r="B22" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2631,7 +2631,7 @@
         <v>135613481</v>
       </c>
       <c r="B20" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>135614695</v>
       </c>
       <c r="B21" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>135614917</v>
       </c>
       <c r="B22" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 26594-2022 artfynd.xlsx
+++ b/artfynd/A 26594-2022 artfynd.xlsx
@@ -2631,7 +2631,7 @@
         <v>135613481</v>
       </c>
       <c r="B20" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>135614695</v>
       </c>
       <c r="B21" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>135614917</v>
       </c>
       <c r="B22" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
